--- a/data/trans_orig/IP19C08-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP19C08-Edad-trans_orig.xlsx
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3725</t>
+          <t>3553</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>12468</t>
+          <t>12294</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>14,78%</t>
+          <t>14,58%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2720</t>
+          <t>2624</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10461</t>
+          <t>10082</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>13,01%</t>
+          <t>12,54%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>7457</t>
+          <t>7814</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>18807</t>
+          <t>19244</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>11,42%</t>
+          <t>11,68%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>71867</t>
+          <t>72041</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>80610</t>
+          <t>80782</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>85,22%</t>
+          <t>85,42%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,58%</t>
+          <t>95,79%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>69957</t>
+          <t>70336</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>77698</t>
+          <t>77794</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>86,99%</t>
+          <t>87,46%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,62%</t>
+          <t>96,74%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>145946</t>
+          <t>145509</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>157296</t>
+          <t>156939</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>88,58%</t>
+          <t>88,32%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,47%</t>
+          <t>95,26%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4156</t>
+          <t>3906</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>13101</t>
+          <t>13389</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>13,21%</t>
+          <t>13,5%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3474</t>
+          <t>3398</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>12073</t>
+          <t>11968</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>11,42%</t>
+          <t>11,32%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>9571</t>
+          <t>9332</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>22046</t>
+          <t>21378</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>10,76%</t>
+          <t>10,43%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>86092</t>
+          <t>85804</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>95037</t>
+          <t>95287</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>86,79%</t>
+          <t>86,5%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>95,81%</t>
+          <t>96,06%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>93646</t>
+          <t>93751</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>102245</t>
+          <t>102321</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>88,58%</t>
+          <t>88,68%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,71%</t>
+          <t>96,79%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>182866</t>
+          <t>183534</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>195341</t>
+          <t>195580</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>89,24%</t>
+          <t>89,57%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,33%</t>
+          <t>95,45%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2489</t>
+          <t>2445</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>9771</t>
+          <t>9142</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2361</t>
+          <t>2411</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>9222</t>
+          <t>9666</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>6233</t>
+          <t>6225</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>15715</t>
+          <t>15984</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1852,7 +1852,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,74%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>153726</t>
+          <t>154355</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>161008</t>
+          <t>161052</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,02%</t>
+          <t>94,41%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,48%</t>
+          <t>98,5%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>164479</t>
+          <t>164035</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>171340</t>
+          <t>171290</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,69%</t>
+          <t>94,44%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,64%</t>
+          <t>98,61%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>321482</t>
+          <t>321213</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>330964</t>
+          <t>330972</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,34%</t>
+          <t>95,26%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>13941</t>
+          <t>13968</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>28110</t>
+          <t>27982</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>7,97%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>11913</t>
+          <t>11336</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>25213</t>
+          <t>24622</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>6,81%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>28943</t>
+          <t>28707</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>50166</t>
+          <t>48048</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>6,74%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>322820</t>
+          <t>322948</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>336989</t>
+          <t>336962</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>91,99%</t>
+          <t>92,03%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,03%</t>
+          <t>96,02%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>336518</t>
+          <t>337109</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>349818</t>
+          <t>350395</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>93,03%</t>
+          <t>93,19%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>96,71%</t>
+          <t>96,87%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>662495</t>
+          <t>664613</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>683718</t>
+          <t>683954</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>92,96%</t>
+          <t>93,26%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,94%</t>
+          <t>95,97%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1882</t>
+          <t>1539</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8816</t>
+          <t>9302</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>11,35%</t>
+          <t>11,97%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2138</t>
+          <t>1987</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>9519</t>
+          <t>9337</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,34%</t>
+          <t>10,14%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>5044</t>
+          <t>4997</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>14747</t>
+          <t>15843</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>9,33%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>68872</t>
+          <t>68386</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>75806</t>
+          <t>76149</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>88,65%</t>
+          <t>88,03%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,58%</t>
+          <t>98,02%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>82545</t>
+          <t>82727</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>89926</t>
+          <t>90077</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>89,66%</t>
+          <t>89,86%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,68%</t>
+          <t>97,84%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>155004</t>
+          <t>153908</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>164707</t>
+          <t>164754</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>91,31%</t>
+          <t>90,67%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,03%</t>
+          <t>97,06%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4270</t>
+          <t>4106</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>13713</t>
+          <t>13736</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>10,96%</t>
+          <t>10,98%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2082</t>
+          <t>2111</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>9919</t>
+          <t>9709</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>7,35%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>7794</t>
+          <t>7600</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>19252</t>
+          <t>19102</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>7,43%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>111373</t>
+          <t>111350</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>120816</t>
+          <t>120980</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>89,04%</t>
+          <t>89,02%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,59%</t>
+          <t>96,72%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>122167</t>
+          <t>122377</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>130004</t>
+          <t>129975</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>92,49%</t>
+          <t>92,65%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,42%</t>
+          <t>98,4%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>237920</t>
+          <t>238070</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>249378</t>
+          <t>249572</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,51%</t>
+          <t>92,57%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,97%</t>
+          <t>97,04%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>675</t>
+          <t>681</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6280</t>
+          <t>7059</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3729,7 +3729,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1401</t>
+          <t>1426</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>8165</t>
+          <t>8346</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3360</t>
+          <t>3401</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>12259</t>
+          <t>12192</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,22%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>141640</t>
+          <t>140861</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>147245</t>
+          <t>147239</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,7 +3837,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,75%</t>
+          <t>95,23%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>133018</t>
+          <t>132837</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>139782</t>
+          <t>139757</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,22%</t>
+          <t>94,09%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,01%</t>
+          <t>98,99%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>276844</t>
+          <t>276911</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>285743</t>
+          <t>285702</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,76%</t>
+          <t>95,78%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,84%</t>
+          <t>98,82%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>9961</t>
+          <t>9148</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>22226</t>
+          <t>21767</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>8871</t>
+          <t>8242</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>20132</t>
+          <t>20937</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>20456</t>
+          <t>20538</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>37950</t>
+          <t>38228</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>5,31%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>331765</t>
+          <t>332224</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>344030</t>
+          <t>344843</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>93,72%</t>
+          <t>93,85%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,19%</t>
+          <t>97,42%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>345870</t>
+          <t>345065</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>357131</t>
+          <t>357760</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>94,5%</t>
+          <t>94,28%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,58%</t>
+          <t>97,75%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>682043</t>
+          <t>681765</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>699537</t>
+          <t>699455</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>94,73%</t>
+          <t>94,69%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,16%</t>
+          <t>97,15%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1648</t>
+          <t>1593</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8253</t>
+          <t>7847</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>12,13%</t>
+          <t>11,53%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5010,7 +5010,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4038</t>
+          <t>4933</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5025,7 +5025,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2324</t>
+          <t>2112</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>9618</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>6,4%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>59807</t>
+          <t>60213</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>66412</t>
+          <t>66467</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>87,87%</t>
+          <t>88,47%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,58%</t>
+          <t>97,66%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,7 +5118,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>78091</t>
+          <t>77196</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -5133,7 +5133,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,08%</t>
+          <t>93,99%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>140189</t>
+          <t>140571</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>147865</t>
+          <t>148077</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,34%</t>
+          <t>93,6%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,45%</t>
+          <t>98,59%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2429</t>
+          <t>2556</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>9753</t>
+          <t>10824</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2805</t>
+          <t>3234</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>10974</t>
+          <t>11045</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>7099</t>
+          <t>7062</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>17832</t>
+          <t>18190</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>6,1%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>139164</t>
+          <t>138093</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>146488</t>
+          <t>146361</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,45%</t>
+          <t>92,73%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,37%</t>
+          <t>98,28%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>138367</t>
+          <t>138296</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>146536</t>
+          <t>146107</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>92,65%</t>
+          <t>92,6%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,12%</t>
+          <t>97,83%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>280426</t>
+          <t>280068</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>291159</t>
+          <t>291196</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,02%</t>
+          <t>93,9%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,62%</t>
+          <t>97,63%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1826</t>
+          <t>1768</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>9251</t>
+          <t>9993</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>6,89%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>715</t>
+          <t>720</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6206</t>
+          <t>6362</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3244</t>
+          <t>3389</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>13659</t>
+          <t>12701</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>4,54%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>135854</t>
+          <t>135112</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>143279</t>
+          <t>143337</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,62%</t>
+          <t>93,11%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,74%</t>
+          <t>98,78%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>128199</t>
+          <t>128043</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>133690</t>
+          <t>133685</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,38%</t>
+          <t>95,27%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,47%</t>
+          <t>99,46%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>265851</t>
+          <t>266809</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>276266</t>
+          <t>276121</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,11%</t>
+          <t>95,46%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,84%</t>
+          <t>98,79%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>8671</t>
+          <t>8625</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>21266</t>
+          <t>21034</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>5302</t>
+          <t>5292</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>15297</t>
+          <t>15409</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6054,7 +6054,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>16612</t>
+          <t>16379</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>31921</t>
+          <t>31571</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,33%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>341352</t>
+          <t>341584</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>353947</t>
+          <t>353993</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>94,14%</t>
+          <t>94,2%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,61%</t>
+          <t>97,62%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>351861</t>
+          <t>351749</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>361856</t>
+          <t>361866</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,7 +6162,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,83%</t>
+          <t>95,8%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>697855</t>
+          <t>698205</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>713164</t>
+          <t>713397</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,63%</t>
+          <t>95,67%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,72%</t>
+          <t>97,76%</t>
         </is>
       </c>
     </row>
@@ -6579,7 +6579,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3046</t>
+          <t>3398</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6594,7 +6594,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>52,54%</t>
+          <t>58,61%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6649,7 +6649,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>3143</t>
+          <t>3737</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6664,7 +6664,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>28,28%</t>
+          <t>33,63%</t>
         </is>
       </c>
     </row>
@@ -6687,7 +6687,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2751</t>
+          <t>2399</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -6702,7 +6702,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>47,46%</t>
+          <t>41,39%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -6757,7 +6757,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>7970</t>
+          <t>7376</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -6772,7 +6772,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>71,72%</t>
+          <t>66,37%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -6917,12 +6917,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>657</t>
+          <t>570</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5887</t>
+          <t>6177</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6932,12 +6932,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>9,33%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6952,12 +6952,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>573</t>
+          <t>563</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5512</t>
+          <t>5210</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6967,12 +6967,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>6,75%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1745</t>
+          <t>1755</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>8066</t>
+          <t>8422</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7007,7 +7007,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,88%</t>
         </is>
       </c>
     </row>
@@ -7030,12 +7030,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>60309</t>
+          <t>60019</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>65539</t>
+          <t>65626</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7045,12 +7045,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>91,11%</t>
+          <t>90,67%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,01%</t>
+          <t>99,14%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7065,12 +7065,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>71619</t>
+          <t>71921</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>76558</t>
+          <t>76568</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7080,12 +7080,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,85%</t>
+          <t>93,25%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,26%</t>
+          <t>99,27%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7100,12 +7100,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>135261</t>
+          <t>134905</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>141582</t>
+          <t>141572</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7115,7 +7115,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,37%</t>
+          <t>94,12%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -7260,12 +7260,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1298</t>
+          <t>1310</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8124</t>
+          <t>8363</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7275,12 +7275,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>6,86%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7295,12 +7295,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2636</t>
+          <t>2834</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>10978</t>
+          <t>12422</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7310,12 +7310,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7330,12 +7330,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>5358</t>
+          <t>5270</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>16283</t>
+          <t>16410</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,72%</t>
         </is>
       </c>
     </row>
@@ -7373,12 +7373,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>113779</t>
+          <t>113540</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>120605</t>
+          <t>120593</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7388,12 +7388,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,34%</t>
+          <t>93,14%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,94%</t>
+          <t>98,93%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7408,12 +7408,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>153810</t>
+          <t>152366</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>162152</t>
+          <t>161954</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,34%</t>
+          <t>92,46%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,4%</t>
+          <t>98,28%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7443,12 +7443,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>270408</t>
+          <t>270281</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>281333</t>
+          <t>281421</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,32%</t>
+          <t>94,28%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,13%</t>
+          <t>98,16%</t>
         </is>
       </c>
     </row>
@@ -7603,12 +7603,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>565</t>
+          <t>556</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5342</t>
+          <t>5185</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7618,12 +7618,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7638,12 +7638,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2587</t>
+          <t>2584</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>24497</t>
+          <t>24808</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7658,7 +7658,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,33%</t>
+          <t>10,46%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7673,12 +7673,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4252</t>
+          <t>4173</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>27242</t>
+          <t>26536</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7688,12 +7688,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,1%</t>
         </is>
       </c>
     </row>
@@ -7716,12 +7716,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>192395</t>
+          <t>192552</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>197172</t>
+          <t>197181</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7731,12 +7731,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,3%</t>
+          <t>97,38%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,71%</t>
+          <t>99,72%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7751,12 +7751,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>212711</t>
+          <t>212400</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>234621</t>
+          <t>234624</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7766,7 +7766,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>89,67%</t>
+          <t>89,54%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -7786,12 +7786,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>407703</t>
+          <t>408409</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>430693</t>
+          <t>430772</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,74%</t>
+          <t>93,9%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,02%</t>
+          <t>99,04%</t>
         </is>
       </c>
     </row>
@@ -7946,12 +7946,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4549</t>
+          <t>4838</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>13992</t>
+          <t>14905</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7961,12 +7961,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7981,12 +7981,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>9080</t>
+          <t>9516</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>32013</t>
+          <t>32833</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>6,78%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8016,12 +8016,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>16461</t>
+          <t>16252</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>39989</t>
+          <t>39753</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,54%</t>
         </is>
       </c>
     </row>
@@ -8059,12 +8059,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>377641</t>
+          <t>376728</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>387084</t>
+          <t>386795</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8074,12 +8074,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>96,43%</t>
+          <t>96,19%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,84%</t>
+          <t>98,76%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8094,12 +8094,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>452431</t>
+          <t>451611</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>475364</t>
+          <t>474928</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8109,12 +8109,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>93,39%</t>
+          <t>93,22%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,13%</t>
+          <t>98,04%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8129,12 +8129,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>836087</t>
+          <t>836323</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>859615</t>
+          <t>859824</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,44%</t>
+          <t>95,46%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,12%</t>
+          <t>98,14%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP19C08-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP19C08-Edad-trans_orig.xlsx
@@ -544,7 +544,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -555,7 +555,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -836,47 +836,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>1893</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>3906</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>1893</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -949,57 +949,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>1893</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>1893</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>1893</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>3906</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>3906</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>3906</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>1893</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>1893</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>1893</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1066,72 +1066,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>5553</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>2671</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>10862</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>6,9%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>3,32%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>13,51%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>7070</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>3553</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>12294</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>3509</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>12082</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>8,38%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>4,21%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>14,58%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>5553</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>2624</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>10082</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>6,9%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>12,54%</t>
+          <t>14,33%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>7814</t>
+          <t>7964</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>19244</t>
+          <t>19396</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>11,68%</t>
+          <t>11,77%</t>
         </is>
       </c>
     </row>
@@ -1179,72 +1179,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>74865</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>69556</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>77747</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>93,1%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>86,49%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>96,68%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>117</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>77265</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>72041</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>80782</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>72253</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>80826</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>91,62%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>85,42%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>95,79%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>115</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>74865</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>70336</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>77794</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>93,1%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>87,46%</t>
+          <t>85,67%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,74%</t>
+          <t>95,84%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>145509</t>
+          <t>145357</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>156939</t>
+          <t>156789</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>88,32%</t>
+          <t>88,23%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,26%</t>
+          <t>95,17%</t>
         </is>
       </c>
     </row>
@@ -1292,57 +1292,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>123</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>80418</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>80418</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>80418</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>127</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>84335</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>84335</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>84335</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>123</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>80418</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>80418</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>80418</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1409,72 +1409,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>6914</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>3639</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>12132</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>6,54%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>3,44%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>11,48%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>7765</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>3906</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>13389</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>4169</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>12975</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>7,83%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>3,94%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>13,5%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>6914</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>3398</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>11968</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>6,54%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>11,32%</t>
+          <t>13,08%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>9332</t>
+          <t>9519</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>21378</t>
+          <t>21615</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>10,55%</t>
         </is>
       </c>
     </row>
@@ -1522,72 +1522,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>148</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>98805</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>93587</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>102080</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>93,46%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>88,52%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>96,56%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>137</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>91428</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>85804</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>95287</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>86218</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>95024</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>92,17%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>86,5%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>96,06%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>148</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>98805</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>93751</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>102321</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>93,46%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>88,68%</t>
+          <t>86,92%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,79%</t>
+          <t>95,8%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>183534</t>
+          <t>183297</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>195580</t>
+          <t>195393</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>89,57%</t>
+          <t>89,45%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,45%</t>
+          <t>95,35%</t>
         </is>
       </c>
     </row>
@@ -1635,57 +1635,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>158</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>105719</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>105719</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>105719</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>148</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>99193</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>99193</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>99193</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>158</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>105719</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>105719</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>105719</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1757,67 +1757,67 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
+          <t>5007</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>2353</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>9609</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>2,88%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>1,35%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>5,53%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
           <t>5200</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>2445</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>9142</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>2013</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>9589</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>3,18%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>1,5%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>5,59%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>5007</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>2411</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>9666</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>2,88%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>6225</t>
+          <t>6074</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>15984</t>
+          <t>15742</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,67%</t>
         </is>
       </c>
     </row>
@@ -1865,72 +1865,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>253</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>168694</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>164092</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>171348</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>97,12%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>94,47%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>98,65%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>233</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>158297</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>154355</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>161052</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>153908</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>161484</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>96,82%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>94,41%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>98,5%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>253</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>168694</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>164035</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>171290</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>97,12%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,44%</t>
+          <t>94,14%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,61%</t>
+          <t>98,77%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>321213</t>
+          <t>321455</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>330972</t>
+          <t>331123</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,26%</t>
+          <t>95,33%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,15%</t>
+          <t>98,2%</t>
         </is>
       </c>
     </row>
@@ -1978,57 +1978,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>261</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>173701</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>173701</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>173701</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>241</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>163497</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>163497</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>163497</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>261</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>173701</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>173701</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>173701</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2095,72 +2095,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>17473</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>11614</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>25056</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>4,83%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>3,21%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>6,93%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>29</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>20035</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>13968</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>27982</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>14335</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>27686</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>5,71%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>3,98%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>7,97%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>17473</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>11336</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>24622</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>4,83%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>7,89%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>28707</t>
+          <t>28877</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>48048</t>
+          <t>48374</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>6,79%</t>
         </is>
       </c>
     </row>
@@ -2208,72 +2208,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>519</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>344258</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>336675</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>350117</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>95,17%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>93,07%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>96,79%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>493</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>330895</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>322948</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>336962</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>323244</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>336595</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>94,29%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>92,03%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>96,02%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>519</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>344258</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>337109</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>350395</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>95,17%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>93,19%</t>
+          <t>92,11%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>96,87%</t>
+          <t>95,92%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>664613</t>
+          <t>664287</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>683954</t>
+          <t>683784</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>93,26%</t>
+          <t>93,21%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,97%</t>
+          <t>95,95%</t>
         </is>
       </c>
     </row>
@@ -2321,57 +2321,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>545</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>361731</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>361731</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>361731</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>522</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>350930</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>350930</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>350930</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>545</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>361731</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>361731</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>361731</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2491,7 +2491,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2502,7 +2502,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2783,47 +2783,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>669</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>3298</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>669</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -2896,57 +2896,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>669</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>669</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>669</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>3298</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>3298</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>3298</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>669</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>669</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>669</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3013,72 +3013,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>4801</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>2010</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>8987</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>5,22%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>2,18%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>9,76%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>4406</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>1539</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>9302</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>1950</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>9245</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>5,67%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>1,98%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>11,97%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>4801</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>1987</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>9337</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>5,22%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,14%</t>
+          <t>11,9%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>4997</t>
+          <t>5112</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>15843</t>
+          <t>15057</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>8,87%</t>
         </is>
       </c>
     </row>
@@ -3126,72 +3126,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>117</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>87263</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>83077</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>90054</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>94,78%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>90,24%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>97,82%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>104</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>73282</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>68386</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>76149</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>68443</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>75738</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>94,33%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>88,03%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>98,02%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>117</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>87263</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>82727</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>90077</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>94,78%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>89,86%</t>
+          <t>88,1%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,84%</t>
+          <t>97,49%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>153908</t>
+          <t>154694</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>164754</t>
+          <t>164639</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>90,67%</t>
+          <t>91,13%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,06%</t>
+          <t>96,99%</t>
         </is>
       </c>
     </row>
@@ -3239,57 +3239,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>124</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>92064</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>92064</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>92064</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>110</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>77688</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>77688</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>77688</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>124</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>92064</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>92064</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>92064</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3356,72 +3356,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>4921</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>2073</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>9584</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>3,73%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>1,57%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>7,26%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>7763</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>4106</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>13736</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>4192</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>12893</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>6,21%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>3,28%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>10,98%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>4921</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>2111</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>9709</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>3,73%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>10,31%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>7600</t>
+          <t>7615</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>19102</t>
+          <t>19886</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3456,7 +3456,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,73%</t>
         </is>
       </c>
     </row>
@@ -3469,72 +3469,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>183</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>127165</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>122502</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>130013</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>96,27%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>92,74%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>98,43%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>167</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>117323</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>111350</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>120980</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>112193</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>120894</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>93,79%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>89,02%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>96,72%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>183</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>127165</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>122377</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>129975</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>96,27%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>92,65%</t>
+          <t>89,69%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,4%</t>
+          <t>96,65%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>238070</t>
+          <t>237286</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>249572</t>
+          <t>249557</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,7 +3564,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,57%</t>
+          <t>92,27%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -3582,57 +3582,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>190</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>132086</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>132086</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>132086</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>178</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>125086</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>125086</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>125086</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>190</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>132086</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>132086</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>132086</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3699,72 +3699,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>4068</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>1414</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>8421</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>2,88%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>1,0%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>5,96%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>2744</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>681</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>7059</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>677</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>6954</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>1,86%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,46%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>4,77%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>4068</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>1426</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>8346</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>2,88%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>1,01%</t>
-        </is>
-      </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3401</t>
+          <t>3413</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>12192</t>
+          <t>11905</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3799,7 +3799,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,12%</t>
         </is>
       </c>
     </row>
@@ -3812,74 +3812,74 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>203</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>137115</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>132762</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>139769</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>97,12%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>94,04%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>99,0%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>207</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>145176</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>140861</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>147239</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>140966</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>147243</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>98,14%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>95,23%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>95,3%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>99,54%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>203</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>137115</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>132837</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>139757</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>97,12%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>94,09%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>98,99%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>410</t>
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>276911</t>
+          <t>277198</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>285702</t>
+          <t>285690</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,7 +3907,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,78%</t>
+          <t>95,88%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -3925,57 +3925,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>209</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>141183</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>141183</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>141183</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>211</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>147920</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>147920</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>147920</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>209</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>141183</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>141183</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>141183</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4042,72 +4042,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>13790</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>8733</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>20159</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>3,77%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>2,39%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>5,51%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>21</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>14912</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>9148</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>21767</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>8974</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>22241</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>4,21%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>2,58%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>6,15%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>13790</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>8242</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>20937</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>3,77%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>20538</t>
+          <t>20870</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>38228</t>
+          <t>37795</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,25%</t>
         </is>
       </c>
     </row>
@@ -4155,72 +4155,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>504</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>352212</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>345843</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>357269</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>96,23%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>94,49%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>97,61%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>483</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>339079</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>332224</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>344843</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>331750</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>345017</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>95,79%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>93,85%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>97,42%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>504</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>352212</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>345065</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>357760</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>96,23%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>94,28%</t>
+          <t>93,72%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,75%</t>
+          <t>97,46%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>681765</t>
+          <t>682198</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>699455</t>
+          <t>699123</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>94,69%</t>
+          <t>94,75%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,15%</t>
+          <t>97,1%</t>
         </is>
       </c>
     </row>
@@ -4268,57 +4268,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>524</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>366002</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>366002</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>366002</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>504</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>353991</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>353991</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>353991</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>524</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>366002</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>366002</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>366002</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4438,7 +4438,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -4449,7 +4449,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -4730,47 +4730,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>1284</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>536</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>1284</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -4843,57 +4843,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>1284</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>1284</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>1284</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>536</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>536</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>536</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>1284</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>1284</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>1284</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4960,72 +4960,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>1248</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>3956</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>1,52%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>4,82%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>3887</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>1593</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>7847</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>1602</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>7998</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>5,71%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>2,34%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>11,53%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>1248</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>4933</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>1,52%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>11,75%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2112</t>
+          <t>2316</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>9618</t>
+          <t>9526</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>6,34%</t>
         </is>
       </c>
     </row>
@@ -5073,72 +5073,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>80881</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>78173</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>82129</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>98,48%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>95,18%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>98</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>64173</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>60213</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>66467</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>60062</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>66458</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>94,29%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>88,47%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>97,66%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>116</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>80881</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>77196</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>82129</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>98,48%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>93,99%</t>
+          <t>88,25%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>97,65%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>140571</t>
+          <t>140663</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>148077</t>
+          <t>147873</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,6%</t>
+          <t>93,66%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,59%</t>
+          <t>98,46%</t>
         </is>
       </c>
     </row>
@@ -5186,57 +5186,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>82129</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>82129</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>82129</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>104</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>68060</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>68060</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>68060</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>118</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>82129</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>82129</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>82129</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5303,72 +5303,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>6137</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>2691</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>11101</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>4,11%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>1,8%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>7,43%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>5428</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>2556</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>10824</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>2445</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>10089</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>3,64%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>1,72%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>7,27%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>6137</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>3234</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>11045</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>4,11%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>7062</t>
+          <t>7033</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>18190</t>
+          <t>18175</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>6,09%</t>
         </is>
       </c>
     </row>
@@ -5416,72 +5416,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>198</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>143204</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>138240</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>146650</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>95,89%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>92,57%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>98,2%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>206</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>143489</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>138093</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>146361</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>138828</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>146472</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>96,36%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>92,73%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>98,28%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>198</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>143204</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>138296</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>146107</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>95,89%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>92,6%</t>
+          <t>93,23%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,83%</t>
+          <t>98,36%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>280068</t>
+          <t>280083</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>291196</t>
+          <t>291225</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>93,9%</t>
+          <t>93,91%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,63%</t>
+          <t>97,64%</t>
         </is>
       </c>
     </row>
@@ -5529,57 +5529,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>207</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>149341</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>149341</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>149341</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>214</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>148917</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>148917</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>148917</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>207</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>149341</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>149341</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>149341</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5646,72 +5646,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>2327</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>719</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>6393</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>1,73%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,53%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>4,76%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>4519</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>1768</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>9993</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>1952</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>9474</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>3,11%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>1,22%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>6,89%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>2327</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>720</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>6362</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>1,73%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>6,53%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3389</t>
+          <t>3383</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>12701</t>
+          <t>12945</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5746,7 +5746,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,63%</t>
         </is>
       </c>
     </row>
@@ -5759,72 +5759,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>179</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>132078</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>128012</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>133686</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>98,27%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>95,24%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>99,47%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>202</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>140586</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>135112</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>143337</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>135631</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>143153</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>96,89%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>93,11%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>98,78%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>179</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>132078</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>128043</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>133685</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>98,27%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,27%</t>
+          <t>93,47%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,46%</t>
+          <t>98,65%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>266809</t>
+          <t>266565</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>276121</t>
+          <t>276127</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,7 +5854,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,46%</t>
+          <t>95,37%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -5872,57 +5872,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>182</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>134405</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>134405</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>134405</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>208</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>145105</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>145105</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>145105</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>182</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>134405</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>134405</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>134405</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5989,72 +5989,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>9713</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>5763</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>16416</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>2,65%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>1,57%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>4,47%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>13833</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>8625</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>21034</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>8650</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>20898</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>3,81%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>2,38%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>5,8%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>9713</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>5292</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>15409</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>2,65%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>16379</t>
+          <t>16009</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>31571</t>
+          <t>31894</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,37%</t>
         </is>
       </c>
     </row>
@@ -6102,72 +6102,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>495</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>357445</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>350742</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>361395</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>97,35%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>95,53%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>98,43%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>507</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>348785</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>341584</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>353993</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>341720</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>353968</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>96,19%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>94,2%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>97,62%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>495</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>357445</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>351749</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>361866</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>97,35%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,8%</t>
+          <t>94,24%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,56%</t>
+          <t>97,61%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>698205</t>
+          <t>697882</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>713397</t>
+          <t>713767</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,67%</t>
+          <t>95,63%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,76%</t>
+          <t>97,81%</t>
         </is>
       </c>
     </row>
@@ -6215,57 +6215,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>509</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>367158</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>367158</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>367158</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>527</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>362618</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>362618</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>362618</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>509</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>367158</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>367158</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>367158</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6385,7 +6385,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -6396,7 +6396,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -6564,107 +6564,107 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>795</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>808</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>3398</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>13,72%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>3134</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>13,3%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>58,61%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>51,62%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>808</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>3068</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>7,51%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>795</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>3737</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>7,16%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>33,63%</t>
+          <t>28,54%</t>
         </is>
       </c>
     </row>
@@ -6677,74 +6677,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>4676</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>5002</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>2399</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>5797</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>86,28%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>41,39%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>5264</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>2938</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>6072</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>86,7%</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>48,38%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>5316</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>18</t>
@@ -6752,27 +6752,27 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>10318</t>
+          <t>9940</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>7376</t>
+          <t>7680</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>11113</t>
+          <t>10748</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>92,84%</t>
+          <t>92,49%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>66,37%</t>
+          <t>71,46%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -6790,57 +6790,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>4676</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>4676</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>4676</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>5797</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>5797</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>5797</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>5316</t>
+          <t>6072</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>5316</t>
+          <t>6072</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>5316</t>
+          <t>6072</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6865,17 +6865,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>11113</t>
+          <t>10748</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>11113</t>
+          <t>10748</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>11113</t>
+          <t>10748</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6907,72 +6907,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>1478</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>427</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>4434</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>2,19%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,63%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>6,56%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>2192</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>570</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>6177</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>3,31%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>0,86%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>9,33%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1863</t>
+          <t>2095</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>563</t>
+          <t>617</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5210</t>
+          <t>5637</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>8,88%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6982,32 +6982,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>4054</t>
+          <t>3574</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1755</t>
+          <t>1690</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>8422</t>
+          <t>7663</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>5,85%</t>
         </is>
       </c>
     </row>
@@ -7020,72 +7020,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>66092</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>63136</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>67143</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>97,81%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>93,44%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>99,37%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>99</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>64004</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>60019</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>65626</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>96,69%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>90,67%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>99,14%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>105</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>75268</t>
+          <t>61354</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>71921</t>
+          <t>57812</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>76568</t>
+          <t>62832</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>97,58%</t>
+          <t>96,7%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>93,25%</t>
+          <t>91,12%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>99,03%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7095,32 +7095,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>139273</t>
+          <t>127446</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>134905</t>
+          <t>123357</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>141572</t>
+          <t>129330</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>97,17%</t>
+          <t>97,27%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,12%</t>
+          <t>94,15%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,78%</t>
+          <t>98,71%</t>
         </is>
       </c>
     </row>
@@ -7133,57 +7133,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>108</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>67570</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>67570</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>67570</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>103</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>66196</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>66196</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>66196</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>108</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>77131</t>
+          <t>63449</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>77131</t>
+          <t>63449</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>77131</t>
+          <t>63449</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7208,17 +7208,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>143327</t>
+          <t>131020</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>143327</t>
+          <t>131020</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>143327</t>
+          <t>131020</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7250,72 +7250,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>5622</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>2584</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>11585</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>3,62%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>1,66%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>7,46%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>3741</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>1310</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>8363</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>3,07%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>1,07%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>6,86%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>5935</t>
+          <t>3747</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2834</t>
+          <t>1185</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>12422</t>
+          <t>8503</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>6,98%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7325,17 +7325,17 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>9676</t>
+          <t>9369</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>5270</t>
+          <t>4721</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>16410</t>
+          <t>15387</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,55%</t>
         </is>
       </c>
     </row>
@@ -7363,72 +7363,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>178</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>149676</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>143713</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>152714</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>96,38%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>92,54%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>98,34%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>158</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>118162</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>113540</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>120593</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>96,93%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>93,14%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>98,93%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>178</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>158853</t>
+          <t>118093</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>152366</t>
+          <t>113337</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>161954</t>
+          <t>120655</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>96,4%</t>
+          <t>96,92%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>92,46%</t>
+          <t>93,02%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,28%</t>
+          <t>99,03%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7438,17 +7438,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>277015</t>
+          <t>267769</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>270281</t>
+          <t>261751</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>281421</t>
+          <t>272417</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,28%</t>
+          <t>94,45%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,16%</t>
+          <t>98,3%</t>
         </is>
       </c>
     </row>
@@ -7476,57 +7476,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>186</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>155298</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>155298</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>155298</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>163</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>121903</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>121903</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>121903</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>186</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>164788</t>
+          <t>121840</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>164788</t>
+          <t>121840</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>164788</t>
+          <t>121840</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7551,17 +7551,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>286691</t>
+          <t>277138</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>286691</t>
+          <t>277138</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>286691</t>
+          <t>277138</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7593,72 +7593,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>8430</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>1965</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>26005</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>3,61%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,84%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>11,13%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>1940</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>556</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>5185</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>0,98%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>1973</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>583</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>5244</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>0,96%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,28%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>2,62%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>8571</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>2584</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>24808</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>3,61%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>1,09%</t>
-        </is>
-      </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,46%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7668,32 +7668,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>10511</t>
+          <t>10403</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4173</t>
+          <t>4275</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>26536</t>
+          <t>26478</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>6,04%</t>
         </is>
       </c>
     </row>
@@ -7706,74 +7706,74 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>263</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>225120</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>207545</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>231585</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>96,39%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>88,87%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>99,16%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>274</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>195797</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>192552</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>197181</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>99,02%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>97,38%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>202943</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>199672</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>204333</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>99,04%</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>97,44%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>99,72%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>263</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>228637</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>212400</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>234624</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>96,39%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>89,54%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>98,91%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>537</t>
@@ -7781,32 +7781,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>424434</t>
+          <t>428063</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>408409</t>
+          <t>411988</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>430772</t>
+          <t>434191</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>97,58%</t>
+          <t>97,63%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,9%</t>
+          <t>93,96%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,04%</t>
+          <t>99,03%</t>
         </is>
       </c>
     </row>
@@ -7819,57 +7819,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>268</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>233550</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>233550</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>233550</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>277</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>197737</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>197737</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>197737</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>268</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>237208</t>
+          <t>204916</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>237208</t>
+          <t>204916</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>237208</t>
+          <t>204916</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7894,17 +7894,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>434945</t>
+          <t>438466</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>434945</t>
+          <t>438466</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>434945</t>
+          <t>438466</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7936,72 +7936,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>15531</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>8342</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>30526</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>3,37%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>1,81%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>6,62%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>8668</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>4838</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>14905</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>2,21%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>1,24%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>3,81%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>16369</t>
+          <t>8623</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>9516</t>
+          <t>4428</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>32833</t>
+          <t>15038</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8011,32 +8011,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>25037</t>
+          <t>24154</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>16252</t>
+          <t>16501</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>39753</t>
+          <t>40308</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,7%</t>
         </is>
       </c>
     </row>
@@ -8049,72 +8049,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>554</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>445564</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>430569</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>452753</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>96,63%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>93,38%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>98,19%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>541</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>382965</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>376728</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>386795</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>97,79%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>96,19%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>98,76%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>554</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>468075</t>
+          <t>387655</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>451611</t>
+          <t>381240</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>474928</t>
+          <t>391850</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>96,62%</t>
+          <t>97,82%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>93,22%</t>
+          <t>96,21%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,04%</t>
+          <t>98,88%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8124,32 +8124,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>851039</t>
+          <t>833218</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>836323</t>
+          <t>817064</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>859824</t>
+          <t>840871</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>97,14%</t>
+          <t>97,18%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,46%</t>
+          <t>95,3%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,14%</t>
+          <t>98,08%</t>
         </is>
       </c>
     </row>
@@ -8162,57 +8162,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>570</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>461095</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>461095</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>461095</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>554</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>391633</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>391633</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>391633</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>570</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>484444</t>
+          <t>396278</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>484444</t>
+          <t>396278</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>484444</t>
+          <t>396278</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8237,17 +8237,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>876076</t>
+          <t>857372</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>876076</t>
+          <t>857372</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>876076</t>
+          <t>857372</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
